--- a/database/FEF1!.xlsx
+++ b/database/FEF1!.xlsx
@@ -417,7 +417,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:F3126"/>
+  <dimension ref="A1:F3127"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -62821,7 +62821,7 @@
         <v>98.8</v>
       </c>
       <c r="E3120" t="n">
-        <v>98.84999999999999</v>
+        <v>99</v>
       </c>
       <c r="F3120" t="n">
         <v>8007</v>
@@ -62841,7 +62841,7 @@
         <v>98.3</v>
       </c>
       <c r="E3121" t="n">
-        <v>98.45</v>
+        <v>98.53</v>
       </c>
       <c r="F3121" t="n">
         <v>5049</v>
@@ -62861,7 +62861,7 @@
         <v>97.90000000000001</v>
       </c>
       <c r="E3122" t="n">
-        <v>98.2</v>
+        <v>97.93000000000001</v>
       </c>
       <c r="F3122" t="n">
         <v>7342</v>
@@ -62881,7 +62881,7 @@
         <v>98.09999999999999</v>
       </c>
       <c r="E3123" t="n">
-        <v>98.2</v>
+        <v>98.23</v>
       </c>
       <c r="F3123" t="n">
         <v>2940</v>
@@ -62944,7 +62944,27 @@
         <v>98.09999999999999</v>
       </c>
       <c r="F3126" t="n">
-        <v>172</v>
+        <v>2350</v>
+      </c>
+    </row>
+    <row r="3127">
+      <c r="A3127" s="1" t="n">
+        <v>46231</v>
+      </c>
+      <c r="B3127" t="n">
+        <v>98.2</v>
+      </c>
+      <c r="C3127" t="n">
+        <v>98.2</v>
+      </c>
+      <c r="D3127" t="n">
+        <v>98.09999999999999</v>
+      </c>
+      <c r="E3127" t="n">
+        <v>98.15000000000001</v>
+      </c>
+      <c r="F3127" t="n">
+        <v>218</v>
       </c>
     </row>
   </sheetData>

--- a/database/FEF1!.xlsx
+++ b/database/FEF1!.xlsx
@@ -62821,7 +62821,7 @@
         <v>98.8</v>
       </c>
       <c r="E3120" t="n">
-        <v>99</v>
+        <v>98.84999999999999</v>
       </c>
       <c r="F3120" t="n">
         <v>8007</v>
@@ -62841,7 +62841,7 @@
         <v>98.3</v>
       </c>
       <c r="E3121" t="n">
-        <v>98.53</v>
+        <v>98.45</v>
       </c>
       <c r="F3121" t="n">
         <v>5049</v>
@@ -62861,7 +62861,7 @@
         <v>97.90000000000001</v>
       </c>
       <c r="E3122" t="n">
-        <v>97.93000000000001</v>
+        <v>98.2</v>
       </c>
       <c r="F3122" t="n">
         <v>7342</v>
@@ -62881,7 +62881,7 @@
         <v>98.09999999999999</v>
       </c>
       <c r="E3123" t="n">
-        <v>98.23</v>
+        <v>98.2</v>
       </c>
       <c r="F3123" t="n">
         <v>2940</v>
@@ -62961,10 +62961,10 @@
         <v>98.09999999999999</v>
       </c>
       <c r="E3127" t="n">
-        <v>98.15000000000001</v>
+        <v>98.2</v>
       </c>
       <c r="F3127" t="n">
-        <v>218</v>
+        <v>241</v>
       </c>
     </row>
   </sheetData>

--- a/database/FEF1!.xlsx
+++ b/database/FEF1!.xlsx
@@ -62821,7 +62821,7 @@
         <v>98.8</v>
       </c>
       <c r="E3120" t="n">
-        <v>98.84999999999999</v>
+        <v>99</v>
       </c>
       <c r="F3120" t="n">
         <v>8007</v>
@@ -62841,7 +62841,7 @@
         <v>98.3</v>
       </c>
       <c r="E3121" t="n">
-        <v>98.45</v>
+        <v>98.53</v>
       </c>
       <c r="F3121" t="n">
         <v>5049</v>
@@ -62861,7 +62861,7 @@
         <v>97.90000000000001</v>
       </c>
       <c r="E3122" t="n">
-        <v>98.2</v>
+        <v>97.93000000000001</v>
       </c>
       <c r="F3122" t="n">
         <v>7342</v>
@@ -62881,7 +62881,7 @@
         <v>98.09999999999999</v>
       </c>
       <c r="E3123" t="n">
-        <v>98.2</v>
+        <v>98.23</v>
       </c>
       <c r="F3123" t="n">
         <v>2940</v>
@@ -62941,7 +62941,7 @@
         <v>98.05</v>
       </c>
       <c r="E3126" t="n">
-        <v>98.09999999999999</v>
+        <v>98.11</v>
       </c>
       <c r="F3126" t="n">
         <v>2350</v>
@@ -62955,7 +62955,7 @@
         <v>98.2</v>
       </c>
       <c r="C3127" t="n">
-        <v>98.2</v>
+        <v>98.25</v>
       </c>
       <c r="D3127" t="n">
         <v>98.09999999999999</v>
@@ -62964,7 +62964,7 @@
         <v>98.2</v>
       </c>
       <c r="F3127" t="n">
-        <v>241</v>
+        <v>2030</v>
       </c>
     </row>
   </sheetData>

--- a/database/FEF1!.xlsx
+++ b/database/FEF1!.xlsx
@@ -417,7 +417,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:F3127"/>
+  <dimension ref="A1:F3128"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -62964,7 +62964,27 @@
         <v>98.2</v>
       </c>
       <c r="F3127" t="n">
-        <v>2030</v>
+        <v>2031</v>
+      </c>
+    </row>
+    <row r="3128">
+      <c r="A3128" s="1" t="n">
+        <v>46232</v>
+      </c>
+      <c r="B3128" t="n">
+        <v>98.15000000000001</v>
+      </c>
+      <c r="C3128" t="n">
+        <v>98.15000000000001</v>
+      </c>
+      <c r="D3128" t="n">
+        <v>98.09999999999999</v>
+      </c>
+      <c r="E3128" t="n">
+        <v>98.09999999999999</v>
+      </c>
+      <c r="F3128" t="n">
+        <v>3255</v>
       </c>
     </row>
   </sheetData>

--- a/database/FEF1!.xlsx
+++ b/database/FEF1!.xlsx
@@ -62941,7 +62941,7 @@
         <v>98.05</v>
       </c>
       <c r="E3126" t="n">
-        <v>98.11</v>
+        <v>98.09999999999999</v>
       </c>
       <c r="F3126" t="n">
         <v>2350</v>

--- a/database/FEF1!.xlsx
+++ b/database/FEF1!.xlsx
@@ -417,7 +417,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:F3128"/>
+  <dimension ref="A1:F3129"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -62941,7 +62941,7 @@
         <v>98.05</v>
       </c>
       <c r="E3126" t="n">
-        <v>98.09999999999999</v>
+        <v>98.11</v>
       </c>
       <c r="F3126" t="n">
         <v>2350</v>
@@ -62978,13 +62978,33 @@
         <v>98.15000000000001</v>
       </c>
       <c r="D3128" t="n">
-        <v>98.09999999999999</v>
+        <v>97.95</v>
       </c>
       <c r="E3128" t="n">
-        <v>98.09999999999999</v>
+        <v>98</v>
       </c>
       <c r="F3128" t="n">
-        <v>3255</v>
+        <v>5597</v>
+      </c>
+    </row>
+    <row r="3129">
+      <c r="A3129" s="1" t="n">
+        <v>46233</v>
+      </c>
+      <c r="B3129" t="n">
+        <v>95.8</v>
+      </c>
+      <c r="C3129" t="n">
+        <v>95.95</v>
+      </c>
+      <c r="D3129" t="n">
+        <v>95.25</v>
+      </c>
+      <c r="E3129" t="n">
+        <v>95.5</v>
+      </c>
+      <c r="F3129" t="n">
+        <v>16822</v>
       </c>
     </row>
   </sheetData>

--- a/database/FEF1!.xlsx
+++ b/database/FEF1!.xlsx
@@ -417,7 +417,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:F3129"/>
+  <dimension ref="A1:F3130"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -62941,7 +62941,7 @@
         <v>98.05</v>
       </c>
       <c r="E3126" t="n">
-        <v>98.11</v>
+        <v>98.09999999999999</v>
       </c>
       <c r="F3126" t="n">
         <v>2350</v>
@@ -62995,16 +62995,36 @@
         <v>95.8</v>
       </c>
       <c r="C3129" t="n">
-        <v>95.95</v>
+        <v>96.55</v>
       </c>
       <c r="D3129" t="n">
-        <v>95.25</v>
+        <v>95.2</v>
       </c>
       <c r="E3129" t="n">
-        <v>95.5</v>
+        <v>95.90000000000001</v>
       </c>
       <c r="F3129" t="n">
-        <v>16822</v>
+        <v>60414</v>
+      </c>
+    </row>
+    <row r="3130">
+      <c r="A3130" s="1" t="n">
+        <v>46234</v>
+      </c>
+      <c r="B3130" t="n">
+        <v>95.84999999999999</v>
+      </c>
+      <c r="C3130" t="n">
+        <v>95.90000000000001</v>
+      </c>
+      <c r="D3130" t="n">
+        <v>94.2</v>
+      </c>
+      <c r="E3130" t="n">
+        <v>94.2</v>
+      </c>
+      <c r="F3130" t="n">
+        <v>27440</v>
       </c>
     </row>
   </sheetData>

--- a/database/FEF1!.xlsx
+++ b/database/FEF1!.xlsx
@@ -417,7 +417,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:F3130"/>
+  <dimension ref="A1:F3131"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -62941,7 +62941,7 @@
         <v>98.05</v>
       </c>
       <c r="E3126" t="n">
-        <v>98.09999999999999</v>
+        <v>98.11</v>
       </c>
       <c r="F3126" t="n">
         <v>2350</v>
@@ -63018,13 +63018,33 @@
         <v>95.90000000000001</v>
       </c>
       <c r="D3130" t="n">
-        <v>94.2</v>
+        <v>93.40000000000001</v>
       </c>
       <c r="E3130" t="n">
-        <v>94.2</v>
+        <v>93.84999999999999</v>
       </c>
       <c r="F3130" t="n">
-        <v>27440</v>
+        <v>60954</v>
+      </c>
+    </row>
+    <row r="3131">
+      <c r="A3131" s="1" t="n">
+        <v>46237</v>
+      </c>
+      <c r="B3131" t="n">
+        <v>93.84999999999999</v>
+      </c>
+      <c r="C3131" t="n">
+        <v>94</v>
+      </c>
+      <c r="D3131" t="n">
+        <v>93.5</v>
+      </c>
+      <c r="E3131" t="n">
+        <v>93.55</v>
+      </c>
+      <c r="F3131" t="n">
+        <v>7454</v>
       </c>
     </row>
   </sheetData>

--- a/database/FEF1!.xlsx
+++ b/database/FEF1!.xlsx
@@ -417,7 +417,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:F3131"/>
+  <dimension ref="A1:F3132"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -63001,7 +63001,7 @@
         <v>95.2</v>
       </c>
       <c r="E3129" t="n">
-        <v>95.90000000000001</v>
+        <v>95.75</v>
       </c>
       <c r="F3129" t="n">
         <v>60414</v>
@@ -63021,7 +63021,7 @@
         <v>93.40000000000001</v>
       </c>
       <c r="E3130" t="n">
-        <v>93.84999999999999</v>
+        <v>93.64</v>
       </c>
       <c r="F3130" t="n">
         <v>60954</v>
@@ -63035,16 +63035,36 @@
         <v>93.84999999999999</v>
       </c>
       <c r="C3131" t="n">
-        <v>94</v>
+        <v>94.09999999999999</v>
       </c>
       <c r="D3131" t="n">
-        <v>93.5</v>
+        <v>92.84999999999999</v>
       </c>
       <c r="E3131" t="n">
+        <v>93.65000000000001</v>
+      </c>
+      <c r="F3131" t="n">
+        <v>31654</v>
+      </c>
+    </row>
+    <row r="3132">
+      <c r="A3132" s="1" t="n">
+        <v>46238</v>
+      </c>
+      <c r="B3132" t="n">
+        <v>93.65000000000001</v>
+      </c>
+      <c r="C3132" t="n">
+        <v>93.8</v>
+      </c>
+      <c r="D3132" t="n">
+        <v>93.45</v>
+      </c>
+      <c r="E3132" t="n">
         <v>93.55</v>
       </c>
-      <c r="F3131" t="n">
-        <v>7454</v>
+      <c r="F3132" t="n">
+        <v>2619</v>
       </c>
     </row>
   </sheetData>

--- a/database/FEF1!.xlsx
+++ b/database/FEF1!.xlsx
@@ -417,7 +417,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:F3132"/>
+  <dimension ref="A1:F3133"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -63001,7 +63001,7 @@
         <v>95.2</v>
       </c>
       <c r="E3129" t="n">
-        <v>95.75</v>
+        <v>95.90000000000001</v>
       </c>
       <c r="F3129" t="n">
         <v>60414</v>
@@ -63021,7 +63021,7 @@
         <v>93.40000000000001</v>
       </c>
       <c r="E3130" t="n">
-        <v>93.64</v>
+        <v>93.84999999999999</v>
       </c>
       <c r="F3130" t="n">
         <v>60954</v>
@@ -63041,7 +63041,7 @@
         <v>92.84999999999999</v>
       </c>
       <c r="E3131" t="n">
-        <v>93.65000000000001</v>
+        <v>93.59999999999999</v>
       </c>
       <c r="F3131" t="n">
         <v>31654</v>
@@ -63055,16 +63055,36 @@
         <v>93.65000000000001</v>
       </c>
       <c r="C3132" t="n">
-        <v>93.8</v>
+        <v>94.25</v>
       </c>
       <c r="D3132" t="n">
-        <v>93.45</v>
+        <v>92.95</v>
       </c>
       <c r="E3132" t="n">
-        <v>93.55</v>
+        <v>94.09999999999999</v>
       </c>
       <c r="F3132" t="n">
-        <v>2619</v>
+        <v>12366</v>
+      </c>
+    </row>
+    <row r="3133">
+      <c r="A3133" s="1" t="n">
+        <v>46239</v>
+      </c>
+      <c r="B3133" t="n">
+        <v>94.15000000000001</v>
+      </c>
+      <c r="C3133" t="n">
+        <v>95.05</v>
+      </c>
+      <c r="D3133" t="n">
+        <v>94.09999999999999</v>
+      </c>
+      <c r="E3133" t="n">
+        <v>94.40000000000001</v>
+      </c>
+      <c r="F3133" t="n">
+        <v>2772</v>
       </c>
     </row>
   </sheetData>

--- a/database/FEF1!.xlsx
+++ b/database/FEF1!.xlsx
@@ -417,7 +417,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:F3133"/>
+  <dimension ref="A1:F3134"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -63075,16 +63075,36 @@
         <v>94.15000000000001</v>
       </c>
       <c r="C3133" t="n">
-        <v>95.05</v>
+        <v>95.90000000000001</v>
       </c>
       <c r="D3133" t="n">
         <v>94.09999999999999</v>
       </c>
       <c r="E3133" t="n">
-        <v>94.40000000000001</v>
+        <v>95.65000000000001</v>
       </c>
       <c r="F3133" t="n">
-        <v>2772</v>
+        <v>23660</v>
+      </c>
+    </row>
+    <row r="3134">
+      <c r="A3134" s="1" t="n">
+        <v>46240</v>
+      </c>
+      <c r="B3134" t="n">
+        <v>95.59999999999999</v>
+      </c>
+      <c r="C3134" t="n">
+        <v>95.65000000000001</v>
+      </c>
+      <c r="D3134" t="n">
+        <v>95.05</v>
+      </c>
+      <c r="E3134" t="n">
+        <v>95.05</v>
+      </c>
+      <c r="F3134" t="n">
+        <v>3240</v>
       </c>
     </row>
   </sheetData>

--- a/database/FEF1!.xlsx
+++ b/database/FEF1!.xlsx
@@ -63101,10 +63101,10 @@
         <v>95.05</v>
       </c>
       <c r="E3134" t="n">
-        <v>95.05</v>
+        <v>95.15000000000001</v>
       </c>
       <c r="F3134" t="n">
-        <v>3240</v>
+        <v>3244</v>
       </c>
     </row>
   </sheetData>

--- a/database/FEF1!.xlsx
+++ b/database/FEF1!.xlsx
@@ -417,7 +417,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:F3134"/>
+  <dimension ref="A1:F3135"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -63098,13 +63098,33 @@
         <v>95.65000000000001</v>
       </c>
       <c r="D3134" t="n">
-        <v>95.05</v>
+        <v>94.59999999999999</v>
       </c>
       <c r="E3134" t="n">
-        <v>95.15000000000001</v>
+        <v>94.7</v>
       </c>
       <c r="F3134" t="n">
-        <v>3244</v>
+        <v>20616</v>
+      </c>
+    </row>
+    <row r="3135">
+      <c r="A3135" s="1" t="n">
+        <v>46241</v>
+      </c>
+      <c r="B3135" t="n">
+        <v>94.7</v>
+      </c>
+      <c r="C3135" t="n">
+        <v>94.84999999999999</v>
+      </c>
+      <c r="D3135" t="n">
+        <v>94.15000000000001</v>
+      </c>
+      <c r="E3135" t="n">
+        <v>94.15000000000001</v>
+      </c>
+      <c r="F3135" t="n">
+        <v>12705</v>
       </c>
     </row>
   </sheetData>

--- a/database/FEF1!.xlsx
+++ b/database/FEF1!.xlsx
@@ -417,7 +417,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:F3135"/>
+  <dimension ref="A1:F3136"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -63001,7 +63001,7 @@
         <v>95.2</v>
       </c>
       <c r="E3129" t="n">
-        <v>95.90000000000001</v>
+        <v>95.75</v>
       </c>
       <c r="F3129" t="n">
         <v>60414</v>
@@ -63021,7 +63021,7 @@
         <v>93.40000000000001</v>
       </c>
       <c r="E3130" t="n">
-        <v>93.84999999999999</v>
+        <v>93.64</v>
       </c>
       <c r="F3130" t="n">
         <v>60954</v>
@@ -63041,7 +63041,7 @@
         <v>92.84999999999999</v>
       </c>
       <c r="E3131" t="n">
-        <v>93.59999999999999</v>
+        <v>93.65000000000001</v>
       </c>
       <c r="F3131" t="n">
         <v>31654</v>
@@ -63115,16 +63115,36 @@
         <v>94.7</v>
       </c>
       <c r="C3135" t="n">
-        <v>94.84999999999999</v>
+        <v>95</v>
       </c>
       <c r="D3135" t="n">
-        <v>94.15000000000001</v>
+        <v>94</v>
       </c>
       <c r="E3135" t="n">
-        <v>94.15000000000001</v>
+        <v>95</v>
       </c>
       <c r="F3135" t="n">
-        <v>12705</v>
+        <v>30160</v>
+      </c>
+    </row>
+    <row r="3136">
+      <c r="A3136" s="1" t="n">
+        <v>46244</v>
+      </c>
+      <c r="B3136" t="n">
+        <v>94.95</v>
+      </c>
+      <c r="C3136" t="n">
+        <v>95.09999999999999</v>
+      </c>
+      <c r="D3136" t="n">
+        <v>94.65000000000001</v>
+      </c>
+      <c r="E3136" t="n">
+        <v>94.95</v>
+      </c>
+      <c r="F3136" t="n">
+        <v>3326</v>
       </c>
     </row>
   </sheetData>

--- a/database/FEF1!.xlsx
+++ b/database/FEF1!.xlsx
@@ -417,7 +417,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:F3136"/>
+  <dimension ref="A1:F3137"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -63081,7 +63081,7 @@
         <v>94.09999999999999</v>
       </c>
       <c r="E3133" t="n">
-        <v>95.65000000000001</v>
+        <v>95.64</v>
       </c>
       <c r="F3133" t="n">
         <v>23660</v>
@@ -63121,7 +63121,7 @@
         <v>94</v>
       </c>
       <c r="E3135" t="n">
-        <v>95</v>
+        <v>94.8</v>
       </c>
       <c r="F3135" t="n">
         <v>30160</v>
@@ -63135,16 +63135,36 @@
         <v>94.95</v>
       </c>
       <c r="C3136" t="n">
-        <v>95.09999999999999</v>
+        <v>95.8</v>
       </c>
       <c r="D3136" t="n">
         <v>94.65000000000001</v>
       </c>
       <c r="E3136" t="n">
-        <v>94.95</v>
+        <v>95.34</v>
       </c>
       <c r="F3136" t="n">
-        <v>3326</v>
+        <v>24554</v>
+      </c>
+    </row>
+    <row r="3137">
+      <c r="A3137" s="1" t="n">
+        <v>46245</v>
+      </c>
+      <c r="B3137" t="n">
+        <v>95.34999999999999</v>
+      </c>
+      <c r="C3137" t="n">
+        <v>95.59999999999999</v>
+      </c>
+      <c r="D3137" t="n">
+        <v>95.34999999999999</v>
+      </c>
+      <c r="E3137" t="n">
+        <v>95.55</v>
+      </c>
+      <c r="F3137" t="n">
+        <v>818</v>
       </c>
     </row>
   </sheetData>

--- a/database/FEF1!.xlsx
+++ b/database/FEF1!.xlsx
@@ -417,7 +417,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:F3137"/>
+  <dimension ref="A1:F3138"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -63155,16 +63155,36 @@
         <v>95.34999999999999</v>
       </c>
       <c r="C3137" t="n">
-        <v>95.59999999999999</v>
+        <v>95.65000000000001</v>
       </c>
       <c r="D3137" t="n">
+        <v>95.05</v>
+      </c>
+      <c r="E3137" t="n">
+        <v>95.45</v>
+      </c>
+      <c r="F3137" t="n">
+        <v>6050</v>
+      </c>
+    </row>
+    <row r="3138">
+      <c r="A3138" s="1" t="n">
+        <v>46246</v>
+      </c>
+      <c r="B3138" t="n">
+        <v>95.40000000000001</v>
+      </c>
+      <c r="C3138" t="n">
+        <v>95.65000000000001</v>
+      </c>
+      <c r="D3138" t="n">
         <v>95.34999999999999</v>
       </c>
-      <c r="E3137" t="n">
+      <c r="E3138" t="n">
         <v>95.55</v>
       </c>
-      <c r="F3137" t="n">
-        <v>818</v>
+      <c r="F3138" t="n">
+        <v>1937</v>
       </c>
     </row>
   </sheetData>

--- a/database/FEF1!.xlsx
+++ b/database/FEF1!.xlsx
@@ -417,7 +417,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:F3138"/>
+  <dimension ref="A1:F3139"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -63141,7 +63141,7 @@
         <v>94.65000000000001</v>
       </c>
       <c r="E3136" t="n">
-        <v>95.34</v>
+        <v>95.40000000000001</v>
       </c>
       <c r="F3136" t="n">
         <v>24554</v>
@@ -63175,16 +63175,36 @@
         <v>95.40000000000001</v>
       </c>
       <c r="C3138" t="n">
-        <v>95.65000000000001</v>
+        <v>95.84999999999999</v>
       </c>
       <c r="D3138" t="n">
-        <v>95.34999999999999</v>
+        <v>95.09999999999999</v>
       </c>
       <c r="E3138" t="n">
-        <v>95.55</v>
+        <v>95.3</v>
       </c>
       <c r="F3138" t="n">
-        <v>1937</v>
+        <v>7217</v>
+      </c>
+    </row>
+    <row r="3139">
+      <c r="A3139" s="1" t="n">
+        <v>46247</v>
+      </c>
+      <c r="B3139" t="n">
+        <v>95.25</v>
+      </c>
+      <c r="C3139" t="n">
+        <v>95.59999999999999</v>
+      </c>
+      <c r="D3139" t="n">
+        <v>95.25</v>
+      </c>
+      <c r="E3139" t="n">
+        <v>95.45</v>
+      </c>
+      <c r="F3139" t="n">
+        <v>2407</v>
       </c>
     </row>
   </sheetData>

--- a/database/FEF1!.xlsx
+++ b/database/FEF1!.xlsx
@@ -417,7 +417,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:F3139"/>
+  <dimension ref="A1:F3140"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -63141,7 +63141,7 @@
         <v>94.65000000000001</v>
       </c>
       <c r="E3136" t="n">
-        <v>95.40000000000001</v>
+        <v>95.34</v>
       </c>
       <c r="F3136" t="n">
         <v>24554</v>
@@ -63161,7 +63161,7 @@
         <v>95.05</v>
       </c>
       <c r="E3137" t="n">
-        <v>95.45</v>
+        <v>95.34999999999999</v>
       </c>
       <c r="F3137" t="n">
         <v>6050</v>
@@ -63181,7 +63181,7 @@
         <v>95.09999999999999</v>
       </c>
       <c r="E3138" t="n">
-        <v>95.3</v>
+        <v>95.14</v>
       </c>
       <c r="F3138" t="n">
         <v>7217</v>
@@ -63195,7 +63195,7 @@
         <v>95.25</v>
       </c>
       <c r="C3139" t="n">
-        <v>95.59999999999999</v>
+        <v>96</v>
       </c>
       <c r="D3139" t="n">
         <v>95.25</v>
@@ -63204,7 +63204,27 @@
         <v>95.45</v>
       </c>
       <c r="F3139" t="n">
-        <v>2407</v>
+        <v>7414</v>
+      </c>
+    </row>
+    <row r="3140">
+      <c r="A3140" s="1" t="n">
+        <v>46248</v>
+      </c>
+      <c r="B3140" t="n">
+        <v>95.45</v>
+      </c>
+      <c r="C3140" t="n">
+        <v>95.5</v>
+      </c>
+      <c r="D3140" t="n">
+        <v>95.15000000000001</v>
+      </c>
+      <c r="E3140" t="n">
+        <v>95.25</v>
+      </c>
+      <c r="F3140" t="n">
+        <v>2583</v>
       </c>
     </row>
   </sheetData>

--- a/database/FEF1!.xlsx
+++ b/database/FEF1!.xlsx
@@ -417,7 +417,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:F3140"/>
+  <dimension ref="A1:F3141"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -63201,7 +63201,7 @@
         <v>95.25</v>
       </c>
       <c r="E3139" t="n">
-        <v>95.45</v>
+        <v>95.5</v>
       </c>
       <c r="F3139" t="n">
         <v>7414</v>
@@ -63215,16 +63215,36 @@
         <v>95.45</v>
       </c>
       <c r="C3140" t="n">
-        <v>95.5</v>
+        <v>95.65000000000001</v>
       </c>
       <c r="D3140" t="n">
-        <v>95.15000000000001</v>
+        <v>95.05</v>
       </c>
       <c r="E3140" t="n">
-        <v>95.25</v>
+        <v>95.09999999999999</v>
       </c>
       <c r="F3140" t="n">
-        <v>2583</v>
+        <v>9217</v>
+      </c>
+    </row>
+    <row r="3141">
+      <c r="A3141" s="1" t="n">
+        <v>46251</v>
+      </c>
+      <c r="B3141" t="n">
+        <v>95.09999999999999</v>
+      </c>
+      <c r="C3141" t="n">
+        <v>95.40000000000001</v>
+      </c>
+      <c r="D3141" t="n">
+        <v>94.7</v>
+      </c>
+      <c r="E3141" t="n">
+        <v>95.09999999999999</v>
+      </c>
+      <c r="F3141" t="n">
+        <v>6888</v>
       </c>
     </row>
   </sheetData>

--- a/database/FEF1!.xlsx
+++ b/database/FEF1!.xlsx
@@ -417,7 +417,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:F3141"/>
+  <dimension ref="A1:F3142"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -63081,7 +63081,7 @@
         <v>94.09999999999999</v>
       </c>
       <c r="E3133" t="n">
-        <v>95.64</v>
+        <v>95.65000000000001</v>
       </c>
       <c r="F3133" t="n">
         <v>23660</v>
@@ -63121,7 +63121,7 @@
         <v>94</v>
       </c>
       <c r="E3135" t="n">
-        <v>94.8</v>
+        <v>95</v>
       </c>
       <c r="F3135" t="n">
         <v>30160</v>
@@ -63141,7 +63141,7 @@
         <v>94.65000000000001</v>
       </c>
       <c r="E3136" t="n">
-        <v>95.34</v>
+        <v>95.40000000000001</v>
       </c>
       <c r="F3136" t="n">
         <v>24554</v>
@@ -63161,7 +63161,7 @@
         <v>95.05</v>
       </c>
       <c r="E3137" t="n">
-        <v>95.34999999999999</v>
+        <v>95.45</v>
       </c>
       <c r="F3137" t="n">
         <v>6050</v>
@@ -63181,7 +63181,7 @@
         <v>95.09999999999999</v>
       </c>
       <c r="E3138" t="n">
-        <v>95.14</v>
+        <v>95.3</v>
       </c>
       <c r="F3138" t="n">
         <v>7217</v>
@@ -63201,7 +63201,7 @@
         <v>95.25</v>
       </c>
       <c r="E3139" t="n">
-        <v>95.5</v>
+        <v>95.45</v>
       </c>
       <c r="F3139" t="n">
         <v>7414</v>
@@ -63221,7 +63221,7 @@
         <v>95.05</v>
       </c>
       <c r="E3140" t="n">
-        <v>95.09999999999999</v>
+        <v>95.05</v>
       </c>
       <c r="F3140" t="n">
         <v>9217</v>
@@ -63235,16 +63235,36 @@
         <v>95.09999999999999</v>
       </c>
       <c r="C3141" t="n">
-        <v>95.40000000000001</v>
+        <v>95.7</v>
       </c>
       <c r="D3141" t="n">
         <v>94.7</v>
       </c>
       <c r="E3141" t="n">
-        <v>95.09999999999999</v>
+        <v>95.59999999999999</v>
       </c>
       <c r="F3141" t="n">
-        <v>6888</v>
+        <v>13509</v>
+      </c>
+    </row>
+    <row r="3142">
+      <c r="A3142" s="1" t="n">
+        <v>46252</v>
+      </c>
+      <c r="B3142" t="n">
+        <v>95.7</v>
+      </c>
+      <c r="C3142" t="n">
+        <v>96</v>
+      </c>
+      <c r="D3142" t="n">
+        <v>95.65000000000001</v>
+      </c>
+      <c r="E3142" t="n">
+        <v>95.75</v>
+      </c>
+      <c r="F3142" t="n">
+        <v>1722</v>
       </c>
     </row>
   </sheetData>

--- a/database/FEF1!.xlsx
+++ b/database/FEF1!.xlsx
@@ -417,7 +417,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:F3142"/>
+  <dimension ref="A1:F3143"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -63258,13 +63258,33 @@
         <v>96</v>
       </c>
       <c r="D3142" t="n">
-        <v>95.65000000000001</v>
+        <v>95.34999999999999</v>
       </c>
       <c r="E3142" t="n">
-        <v>95.75</v>
+        <v>95.34999999999999</v>
       </c>
       <c r="F3142" t="n">
-        <v>1722</v>
+        <v>6015</v>
+      </c>
+    </row>
+    <row r="3143">
+      <c r="A3143" s="1" t="n">
+        <v>46253</v>
+      </c>
+      <c r="B3143" t="n">
+        <v>95.34999999999999</v>
+      </c>
+      <c r="C3143" t="n">
+        <v>95.5</v>
+      </c>
+      <c r="D3143" t="n">
+        <v>95.34999999999999</v>
+      </c>
+      <c r="E3143" t="n">
+        <v>95.40000000000001</v>
+      </c>
+      <c r="F3143" t="n">
+        <v>2059</v>
       </c>
     </row>
   </sheetData>

--- a/database/FEF1!.xlsx
+++ b/database/FEF1!.xlsx
@@ -417,7 +417,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:F3143"/>
+  <dimension ref="A1:F3144"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -63081,7 +63081,7 @@
         <v>94.09999999999999</v>
       </c>
       <c r="E3133" t="n">
-        <v>95.65000000000001</v>
+        <v>95.64</v>
       </c>
       <c r="F3133" t="n">
         <v>23660</v>
@@ -63121,7 +63121,7 @@
         <v>94</v>
       </c>
       <c r="E3135" t="n">
-        <v>95</v>
+        <v>94.8</v>
       </c>
       <c r="F3135" t="n">
         <v>30160</v>
@@ -63278,13 +63278,33 @@
         <v>95.5</v>
       </c>
       <c r="D3143" t="n">
+        <v>95</v>
+      </c>
+      <c r="E3143" t="n">
         <v>95.34999999999999</v>
       </c>
-      <c r="E3143" t="n">
+      <c r="F3143" t="n">
+        <v>9119</v>
+      </c>
+    </row>
+    <row r="3144">
+      <c r="A3144" s="1" t="n">
+        <v>46254</v>
+      </c>
+      <c r="B3144" t="n">
         <v>95.40000000000001</v>
       </c>
-      <c r="F3143" t="n">
-        <v>2059</v>
+      <c r="C3144" t="n">
+        <v>95.5</v>
+      </c>
+      <c r="D3144" t="n">
+        <v>95.15000000000001</v>
+      </c>
+      <c r="E3144" t="n">
+        <v>95.15000000000001</v>
+      </c>
+      <c r="F3144" t="n">
+        <v>360</v>
       </c>
     </row>
   </sheetData>

--- a/database/FEF1!.xlsx
+++ b/database/FEF1!.xlsx
@@ -417,7 +417,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:F3144"/>
+  <dimension ref="A1:F3145"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -63141,7 +63141,7 @@
         <v>94.65000000000001</v>
       </c>
       <c r="E3136" t="n">
-        <v>95.40000000000001</v>
+        <v>95.34</v>
       </c>
       <c r="F3136" t="n">
         <v>24554</v>
@@ -63161,7 +63161,7 @@
         <v>95.05</v>
       </c>
       <c r="E3137" t="n">
-        <v>95.45</v>
+        <v>95.34999999999999</v>
       </c>
       <c r="F3137" t="n">
         <v>6050</v>
@@ -63181,7 +63181,7 @@
         <v>95.09999999999999</v>
       </c>
       <c r="E3138" t="n">
-        <v>95.3</v>
+        <v>95.14</v>
       </c>
       <c r="F3138" t="n">
         <v>7217</v>
@@ -63201,7 +63201,7 @@
         <v>95.25</v>
       </c>
       <c r="E3139" t="n">
-        <v>95.45</v>
+        <v>95.5</v>
       </c>
       <c r="F3139" t="n">
         <v>7414</v>
@@ -63295,16 +63295,36 @@
         <v>95.40000000000001</v>
       </c>
       <c r="C3144" t="n">
-        <v>95.5</v>
+        <v>95.59999999999999</v>
       </c>
       <c r="D3144" t="n">
         <v>95.15000000000001</v>
       </c>
       <c r="E3144" t="n">
-        <v>95.15000000000001</v>
+        <v>95.45</v>
       </c>
       <c r="F3144" t="n">
-        <v>360</v>
+        <v>3192</v>
+      </c>
+    </row>
+    <row r="3145">
+      <c r="A3145" s="1" t="n">
+        <v>46255</v>
+      </c>
+      <c r="B3145" t="n">
+        <v>95.40000000000001</v>
+      </c>
+      <c r="C3145" t="n">
+        <v>95.65000000000001</v>
+      </c>
+      <c r="D3145" t="n">
+        <v>95.40000000000001</v>
+      </c>
+      <c r="E3145" t="n">
+        <v>95.65000000000001</v>
+      </c>
+      <c r="F3145" t="n">
+        <v>422</v>
       </c>
     </row>
   </sheetData>

--- a/database/FEF1!.xlsx
+++ b/database/FEF1!.xlsx
@@ -417,7 +417,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:F3145"/>
+  <dimension ref="A1:F3146"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -63221,7 +63221,7 @@
         <v>95.05</v>
       </c>
       <c r="E3140" t="n">
-        <v>95.05</v>
+        <v>95.09999999999999</v>
       </c>
       <c r="F3140" t="n">
         <v>9217</v>
@@ -63261,7 +63261,7 @@
         <v>95.34999999999999</v>
       </c>
       <c r="E3142" t="n">
-        <v>95.34999999999999</v>
+        <v>95.36</v>
       </c>
       <c r="F3142" t="n">
         <v>6015</v>
@@ -63281,7 +63281,7 @@
         <v>95</v>
       </c>
       <c r="E3143" t="n">
-        <v>95.34999999999999</v>
+        <v>95.31</v>
       </c>
       <c r="F3143" t="n">
         <v>9119</v>
@@ -63301,7 +63301,7 @@
         <v>95.15000000000001</v>
       </c>
       <c r="E3144" t="n">
-        <v>95.45</v>
+        <v>95.33</v>
       </c>
       <c r="F3144" t="n">
         <v>3192</v>
@@ -63315,16 +63315,36 @@
         <v>95.40000000000001</v>
       </c>
       <c r="C3145" t="n">
-        <v>95.65000000000001</v>
+        <v>96.05</v>
       </c>
       <c r="D3145" t="n">
         <v>95.40000000000001</v>
       </c>
       <c r="E3145" t="n">
-        <v>95.65000000000001</v>
+        <v>95.90000000000001</v>
       </c>
       <c r="F3145" t="n">
-        <v>422</v>
+        <v>4471</v>
+      </c>
+    </row>
+    <row r="3146">
+      <c r="A3146" s="1" t="n">
+        <v>46258</v>
+      </c>
+      <c r="B3146" t="n">
+        <v>95.95</v>
+      </c>
+      <c r="C3146" t="n">
+        <v>95.95</v>
+      </c>
+      <c r="D3146" t="n">
+        <v>95.8</v>
+      </c>
+      <c r="E3146" t="n">
+        <v>95.8</v>
+      </c>
+      <c r="F3146" t="n">
+        <v>390</v>
       </c>
     </row>
   </sheetData>

--- a/database/FEF1!.xlsx
+++ b/database/FEF1!.xlsx
@@ -417,7 +417,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:F3146"/>
+  <dimension ref="A1:F3147"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -63301,7 +63301,7 @@
         <v>95.15000000000001</v>
       </c>
       <c r="E3144" t="n">
-        <v>95.33</v>
+        <v>95.45</v>
       </c>
       <c r="F3144" t="n">
         <v>3192</v>
@@ -63338,13 +63338,33 @@
         <v>95.95</v>
       </c>
       <c r="D3146" t="n">
-        <v>95.8</v>
+        <v>95.59999999999999</v>
       </c>
       <c r="E3146" t="n">
-        <v>95.8</v>
+        <v>95.75</v>
       </c>
       <c r="F3146" t="n">
-        <v>390</v>
+        <v>5227</v>
+      </c>
+    </row>
+    <row r="3147">
+      <c r="A3147" s="1" t="n">
+        <v>46259</v>
+      </c>
+      <c r="B3147" t="n">
+        <v>95.84999999999999</v>
+      </c>
+      <c r="C3147" t="n">
+        <v>95.84999999999999</v>
+      </c>
+      <c r="D3147" t="n">
+        <v>95.7</v>
+      </c>
+      <c r="E3147" t="n">
+        <v>95.7</v>
+      </c>
+      <c r="F3147" t="n">
+        <v>8</v>
       </c>
     </row>
   </sheetData>

--- a/database/FEF1!.xlsx
+++ b/database/FEF1!.xlsx
@@ -417,7 +417,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:F3147"/>
+  <dimension ref="A1:F3148"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -63301,7 +63301,7 @@
         <v>95.15000000000001</v>
       </c>
       <c r="E3144" t="n">
-        <v>95.45</v>
+        <v>95.33</v>
       </c>
       <c r="F3144" t="n">
         <v>3192</v>
@@ -63355,16 +63355,36 @@
         <v>95.84999999999999</v>
       </c>
       <c r="C3147" t="n">
-        <v>95.84999999999999</v>
+        <v>96</v>
       </c>
       <c r="D3147" t="n">
         <v>95.7</v>
       </c>
       <c r="E3147" t="n">
-        <v>95.7</v>
+        <v>95.95</v>
       </c>
       <c r="F3147" t="n">
-        <v>8</v>
+        <v>4635</v>
+      </c>
+    </row>
+    <row r="3148">
+      <c r="A3148" s="1" t="n">
+        <v>46260</v>
+      </c>
+      <c r="B3148" t="n">
+        <v>95.95</v>
+      </c>
+      <c r="C3148" t="n">
+        <v>95.95</v>
+      </c>
+      <c r="D3148" t="n">
+        <v>95.90000000000001</v>
+      </c>
+      <c r="E3148" t="n">
+        <v>95.90000000000001</v>
+      </c>
+      <c r="F3148" t="n">
+        <v>631</v>
       </c>
     </row>
   </sheetData>

--- a/database/FEF1!.xlsx
+++ b/database/FEF1!.xlsx
@@ -417,7 +417,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:F3148"/>
+  <dimension ref="A1:F3149"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -63301,7 +63301,7 @@
         <v>95.15000000000001</v>
       </c>
       <c r="E3144" t="n">
-        <v>95.33</v>
+        <v>95.45</v>
       </c>
       <c r="F3144" t="n">
         <v>3192</v>
@@ -63375,16 +63375,36 @@
         <v>95.95</v>
       </c>
       <c r="C3148" t="n">
-        <v>95.95</v>
+        <v>96</v>
       </c>
       <c r="D3148" t="n">
-        <v>95.90000000000001</v>
+        <v>95.84999999999999</v>
       </c>
       <c r="E3148" t="n">
         <v>95.90000000000001</v>
       </c>
       <c r="F3148" t="n">
-        <v>631</v>
+        <v>2521</v>
+      </c>
+    </row>
+    <row r="3149">
+      <c r="A3149" s="1" t="n">
+        <v>46261</v>
+      </c>
+      <c r="B3149" t="n">
+        <v>95.90000000000001</v>
+      </c>
+      <c r="C3149" t="n">
+        <v>96</v>
+      </c>
+      <c r="D3149" t="n">
+        <v>95.90000000000001</v>
+      </c>
+      <c r="E3149" t="n">
+        <v>95.95</v>
+      </c>
+      <c r="F3149" t="n">
+        <v>818</v>
       </c>
     </row>
   </sheetData>

--- a/database/FEF1!.xlsx
+++ b/database/FEF1!.xlsx
@@ -417,7 +417,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:F3149"/>
+  <dimension ref="A1:F3150"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -63301,7 +63301,7 @@
         <v>95.15000000000001</v>
       </c>
       <c r="E3144" t="n">
-        <v>95.45</v>
+        <v>95.33</v>
       </c>
       <c r="F3144" t="n">
         <v>3192</v>
@@ -63404,7 +63404,27 @@
         <v>95.95</v>
       </c>
       <c r="F3149" t="n">
-        <v>818</v>
+        <v>5210</v>
+      </c>
+    </row>
+    <row r="3150">
+      <c r="A3150" s="1" t="n">
+        <v>46262</v>
+      </c>
+      <c r="B3150" t="n">
+        <v>98.8</v>
+      </c>
+      <c r="C3150" t="n">
+        <v>99.05</v>
+      </c>
+      <c r="D3150" t="n">
+        <v>98.65000000000001</v>
+      </c>
+      <c r="E3150" t="n">
+        <v>99</v>
+      </c>
+      <c r="F3150" t="n">
+        <v>18892</v>
       </c>
     </row>
   </sheetData>

--- a/database/FEF1!.xlsx
+++ b/database/FEF1!.xlsx
@@ -63421,10 +63421,10 @@
         <v>98.65000000000001</v>
       </c>
       <c r="E3150" t="n">
-        <v>99</v>
+        <v>98.95</v>
       </c>
       <c r="F3150" t="n">
-        <v>18892</v>
+        <v>19025</v>
       </c>
     </row>
   </sheetData>

--- a/database/FEF1!.xlsx
+++ b/database/FEF1!.xlsx
@@ -63301,7 +63301,7 @@
         <v>95.15000000000001</v>
       </c>
       <c r="E3144" t="n">
-        <v>95.33</v>
+        <v>95.45</v>
       </c>
       <c r="F3144" t="n">
         <v>3192</v>

--- a/database/FEF1!.xlsx
+++ b/database/FEF1!.xlsx
@@ -417,7 +417,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:F3150"/>
+  <dimension ref="A1:F3152"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -63301,7 +63301,7 @@
         <v>95.15000000000001</v>
       </c>
       <c r="E3144" t="n">
-        <v>95.45</v>
+        <v>95.33</v>
       </c>
       <c r="F3144" t="n">
         <v>3192</v>
@@ -63341,7 +63341,7 @@
         <v>95.59999999999999</v>
       </c>
       <c r="E3146" t="n">
-        <v>95.75</v>
+        <v>95.7</v>
       </c>
       <c r="F3146" t="n">
         <v>5227</v>
@@ -63361,7 +63361,7 @@
         <v>95.7</v>
       </c>
       <c r="E3147" t="n">
-        <v>95.95</v>
+        <v>96</v>
       </c>
       <c r="F3147" t="n">
         <v>4635</v>
@@ -63381,7 +63381,7 @@
         <v>95.84999999999999</v>
       </c>
       <c r="E3148" t="n">
-        <v>95.90000000000001</v>
+        <v>95.92</v>
       </c>
       <c r="F3148" t="n">
         <v>2521</v>
@@ -63401,7 +63401,7 @@
         <v>95.90000000000001</v>
       </c>
       <c r="E3149" t="n">
-        <v>95.95</v>
+        <v>96</v>
       </c>
       <c r="F3149" t="n">
         <v>5210</v>
@@ -63415,16 +63415,56 @@
         <v>98.8</v>
       </c>
       <c r="C3150" t="n">
-        <v>99.05</v>
+        <v>99.75</v>
       </c>
       <c r="D3150" t="n">
         <v>98.65000000000001</v>
       </c>
       <c r="E3150" t="n">
-        <v>98.95</v>
+        <v>99.59999999999999</v>
       </c>
       <c r="F3150" t="n">
-        <v>19025</v>
+        <v>104149</v>
+      </c>
+    </row>
+    <row r="3151">
+      <c r="A3151" s="1" t="n">
+        <v>46265</v>
+      </c>
+      <c r="B3151" t="n">
+        <v>99.2</v>
+      </c>
+      <c r="C3151" t="n">
+        <v>99.75</v>
+      </c>
+      <c r="D3151" t="n">
+        <v>98.75</v>
+      </c>
+      <c r="E3151" t="n">
+        <v>99.5</v>
+      </c>
+      <c r="F3151" t="n">
+        <v>64279</v>
+      </c>
+    </row>
+    <row r="3152">
+      <c r="A3152" s="1" t="n">
+        <v>46266</v>
+      </c>
+      <c r="B3152" t="n">
+        <v>99.45</v>
+      </c>
+      <c r="C3152" t="n">
+        <v>99.55</v>
+      </c>
+      <c r="D3152" t="n">
+        <v>98.90000000000001</v>
+      </c>
+      <c r="E3152" t="n">
+        <v>99.2</v>
+      </c>
+      <c r="F3152" t="n">
+        <v>6299</v>
       </c>
     </row>
   </sheetData>

--- a/database/FEF1!.xlsx
+++ b/database/FEF1!.xlsx
@@ -417,7 +417,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:F3152"/>
+  <dimension ref="A1:F3153"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -63421,7 +63421,7 @@
         <v>98.65000000000001</v>
       </c>
       <c r="E3150" t="n">
-        <v>99.59999999999999</v>
+        <v>99.65000000000001</v>
       </c>
       <c r="F3150" t="n">
         <v>104149</v>
@@ -63441,7 +63441,7 @@
         <v>98.75</v>
       </c>
       <c r="E3151" t="n">
-        <v>99.5</v>
+        <v>99.34999999999999</v>
       </c>
       <c r="F3151" t="n">
         <v>64279</v>
@@ -63458,13 +63458,33 @@
         <v>99.55</v>
       </c>
       <c r="D3152" t="n">
-        <v>98.90000000000001</v>
+        <v>97.55</v>
       </c>
       <c r="E3152" t="n">
-        <v>99.2</v>
+        <v>97.90000000000001</v>
       </c>
       <c r="F3152" t="n">
-        <v>6299</v>
+        <v>46263</v>
+      </c>
+    </row>
+    <row r="3153">
+      <c r="A3153" s="1" t="n">
+        <v>46267</v>
+      </c>
+      <c r="B3153" t="n">
+        <v>98.05</v>
+      </c>
+      <c r="C3153" t="n">
+        <v>98.34999999999999</v>
+      </c>
+      <c r="D3153" t="n">
+        <v>97.75</v>
+      </c>
+      <c r="E3153" t="n">
+        <v>98.15000000000001</v>
+      </c>
+      <c r="F3153" t="n">
+        <v>5975</v>
       </c>
     </row>
   </sheetData>

--- a/database/FEF1!.xlsx
+++ b/database/FEF1!.xlsx
@@ -417,7 +417,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:F3153"/>
+  <dimension ref="A1:F3154"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -63475,16 +63475,36 @@
         <v>98.05</v>
       </c>
       <c r="C3153" t="n">
-        <v>98.34999999999999</v>
+        <v>99.7</v>
       </c>
       <c r="D3153" t="n">
         <v>97.75</v>
       </c>
       <c r="E3153" t="n">
-        <v>98.15000000000001</v>
+        <v>99.2</v>
       </c>
       <c r="F3153" t="n">
-        <v>5975</v>
+        <v>31168</v>
+      </c>
+    </row>
+    <row r="3154">
+      <c r="A3154" s="1" t="n">
+        <v>46268</v>
+      </c>
+      <c r="B3154" t="n">
+        <v>99.34999999999999</v>
+      </c>
+      <c r="C3154" t="n">
+        <v>99.40000000000001</v>
+      </c>
+      <c r="D3154" t="n">
+        <v>98.8</v>
+      </c>
+      <c r="E3154" t="n">
+        <v>98.8</v>
+      </c>
+      <c r="F3154" t="n">
+        <v>5461</v>
       </c>
     </row>
   </sheetData>

--- a/database/FEF1!.xlsx
+++ b/database/FEF1!.xlsx
@@ -417,7 +417,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:F3154"/>
+  <dimension ref="A1:F3155"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -63495,16 +63495,36 @@
         <v>99.34999999999999</v>
       </c>
       <c r="C3154" t="n">
-        <v>99.40000000000001</v>
+        <v>100</v>
       </c>
       <c r="D3154" t="n">
         <v>98.8</v>
       </c>
       <c r="E3154" t="n">
-        <v>98.8</v>
+        <v>99.95</v>
       </c>
       <c r="F3154" t="n">
-        <v>5461</v>
+        <v>48993</v>
+      </c>
+    </row>
+    <row r="3155">
+      <c r="A3155" s="1" t="n">
+        <v>46269</v>
+      </c>
+      <c r="B3155" t="n">
+        <v>99.95</v>
+      </c>
+      <c r="C3155" t="n">
+        <v>100.5</v>
+      </c>
+      <c r="D3155" t="n">
+        <v>99.84999999999999</v>
+      </c>
+      <c r="E3155" t="n">
+        <v>100.35</v>
+      </c>
+      <c r="F3155" t="n">
+        <v>12291</v>
       </c>
     </row>
   </sheetData>

--- a/database/FEF1!.xlsx
+++ b/database/FEF1!.xlsx
@@ -417,7 +417,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:F3155"/>
+  <dimension ref="A1:F3156"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -63421,7 +63421,7 @@
         <v>98.65000000000001</v>
       </c>
       <c r="E3150" t="n">
-        <v>99.65000000000001</v>
+        <v>99.59999999999999</v>
       </c>
       <c r="F3150" t="n">
         <v>104149</v>
@@ -63441,7 +63441,7 @@
         <v>98.75</v>
       </c>
       <c r="E3151" t="n">
-        <v>99.34999999999999</v>
+        <v>99.5</v>
       </c>
       <c r="F3151" t="n">
         <v>64279</v>
@@ -63461,7 +63461,7 @@
         <v>97.55</v>
       </c>
       <c r="E3152" t="n">
-        <v>97.90000000000001</v>
+        <v>97.55</v>
       </c>
       <c r="F3152" t="n">
         <v>46263</v>
@@ -63481,7 +63481,7 @@
         <v>97.75</v>
       </c>
       <c r="E3153" t="n">
-        <v>99.2</v>
+        <v>99.34999999999999</v>
       </c>
       <c r="F3153" t="n">
         <v>31168</v>
@@ -63501,7 +63501,7 @@
         <v>98.8</v>
       </c>
       <c r="E3154" t="n">
-        <v>99.95</v>
+        <v>99.65000000000001</v>
       </c>
       <c r="F3154" t="n">
         <v>48993</v>
@@ -63515,16 +63515,36 @@
         <v>99.95</v>
       </c>
       <c r="C3155" t="n">
-        <v>100.5</v>
+        <v>100.9</v>
       </c>
       <c r="D3155" t="n">
         <v>99.84999999999999</v>
       </c>
       <c r="E3155" t="n">
+        <v>100.4</v>
+      </c>
+      <c r="F3155" t="n">
+        <v>41136</v>
+      </c>
+    </row>
+    <row r="3156">
+      <c r="A3156" s="1" t="n">
+        <v>46272</v>
+      </c>
+      <c r="B3156" t="n">
         <v>100.35</v>
       </c>
-      <c r="F3155" t="n">
-        <v>12291</v>
+      <c r="C3156" t="n">
+        <v>100.8</v>
+      </c>
+      <c r="D3156" t="n">
+        <v>100.2</v>
+      </c>
+      <c r="E3156" t="n">
+        <v>100.45</v>
+      </c>
+      <c r="F3156" t="n">
+        <v>7619</v>
       </c>
     </row>
   </sheetData>

--- a/database/FEF1!.xlsx
+++ b/database/FEF1!.xlsx
@@ -417,7 +417,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:F3156"/>
+  <dimension ref="A1:F3157"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -63421,7 +63421,7 @@
         <v>98.65000000000001</v>
       </c>
       <c r="E3150" t="n">
-        <v>99.59999999999999</v>
+        <v>99.65000000000001</v>
       </c>
       <c r="F3150" t="n">
         <v>104149</v>
@@ -63441,7 +63441,7 @@
         <v>98.75</v>
       </c>
       <c r="E3151" t="n">
-        <v>99.5</v>
+        <v>99.34999999999999</v>
       </c>
       <c r="F3151" t="n">
         <v>64279</v>
@@ -63461,7 +63461,7 @@
         <v>97.55</v>
       </c>
       <c r="E3152" t="n">
-        <v>97.55</v>
+        <v>97.90000000000001</v>
       </c>
       <c r="F3152" t="n">
         <v>46263</v>
@@ -63481,7 +63481,7 @@
         <v>97.75</v>
       </c>
       <c r="E3153" t="n">
-        <v>99.34999999999999</v>
+        <v>99.2</v>
       </c>
       <c r="F3153" t="n">
         <v>31168</v>
@@ -63501,7 +63501,7 @@
         <v>98.8</v>
       </c>
       <c r="E3154" t="n">
-        <v>99.65000000000001</v>
+        <v>99.95</v>
       </c>
       <c r="F3154" t="n">
         <v>48993</v>
@@ -63535,16 +63535,36 @@
         <v>100.35</v>
       </c>
       <c r="C3156" t="n">
-        <v>100.8</v>
+        <v>100.9</v>
       </c>
       <c r="D3156" t="n">
+        <v>99.8</v>
+      </c>
+      <c r="E3156" t="n">
         <v>100.2</v>
       </c>
-      <c r="E3156" t="n">
-        <v>100.45</v>
-      </c>
       <c r="F3156" t="n">
-        <v>7619</v>
+        <v>33873</v>
+      </c>
+    </row>
+    <row r="3157">
+      <c r="A3157" s="1" t="n">
+        <v>46273</v>
+      </c>
+      <c r="B3157" t="n">
+        <v>100.2</v>
+      </c>
+      <c r="C3157" t="n">
+        <v>100.3</v>
+      </c>
+      <c r="D3157" t="n">
+        <v>99.84999999999999</v>
+      </c>
+      <c r="E3157" t="n">
+        <v>99.84999999999999</v>
+      </c>
+      <c r="F3157" t="n">
+        <v>1174</v>
       </c>
     </row>
   </sheetData>

--- a/database/FEF1!.xlsx
+++ b/database/FEF1!.xlsx
@@ -417,7 +417,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:F3157"/>
+  <dimension ref="A1:F3158"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -63421,7 +63421,7 @@
         <v>98.65000000000001</v>
       </c>
       <c r="E3150" t="n">
-        <v>99.65000000000001</v>
+        <v>99.59999999999999</v>
       </c>
       <c r="F3150" t="n">
         <v>104149</v>
@@ -63441,7 +63441,7 @@
         <v>98.75</v>
       </c>
       <c r="E3151" t="n">
-        <v>99.34999999999999</v>
+        <v>99.5</v>
       </c>
       <c r="F3151" t="n">
         <v>64279</v>
@@ -63461,7 +63461,7 @@
         <v>97.55</v>
       </c>
       <c r="E3152" t="n">
-        <v>97.90000000000001</v>
+        <v>97.55</v>
       </c>
       <c r="F3152" t="n">
         <v>46263</v>
@@ -63481,7 +63481,7 @@
         <v>97.75</v>
       </c>
       <c r="E3153" t="n">
-        <v>99.2</v>
+        <v>99.34999999999999</v>
       </c>
       <c r="F3153" t="n">
         <v>31168</v>
@@ -63501,7 +63501,7 @@
         <v>98.8</v>
       </c>
       <c r="E3154" t="n">
-        <v>99.95</v>
+        <v>99.65000000000001</v>
       </c>
       <c r="F3154" t="n">
         <v>48993</v>
@@ -63558,13 +63558,33 @@
         <v>100.3</v>
       </c>
       <c r="D3157" t="n">
-        <v>99.84999999999999</v>
+        <v>99.09999999999999</v>
       </c>
       <c r="E3157" t="n">
-        <v>99.84999999999999</v>
+        <v>99.34999999999999</v>
       </c>
       <c r="F3157" t="n">
-        <v>1174</v>
+        <v>8092</v>
+      </c>
+    </row>
+    <row r="3158">
+      <c r="A3158" s="1" t="n">
+        <v>46274</v>
+      </c>
+      <c r="B3158" t="n">
+        <v>99.34999999999999</v>
+      </c>
+      <c r="C3158" t="n">
+        <v>99.40000000000001</v>
+      </c>
+      <c r="D3158" t="n">
+        <v>99.05</v>
+      </c>
+      <c r="E3158" t="n">
+        <v>99.05</v>
+      </c>
+      <c r="F3158" t="n">
+        <v>2906</v>
       </c>
     </row>
   </sheetData>

--- a/database/FEF1!.xlsx
+++ b/database/FEF1!.xlsx
@@ -417,7 +417,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:F3158"/>
+  <dimension ref="A1:F3159"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -63521,7 +63521,7 @@
         <v>99.84999999999999</v>
       </c>
       <c r="E3155" t="n">
-        <v>100.4</v>
+        <v>100.26</v>
       </c>
       <c r="F3155" t="n">
         <v>41136</v>
@@ -63541,7 +63541,7 @@
         <v>99.8</v>
       </c>
       <c r="E3156" t="n">
-        <v>100.2</v>
+        <v>100.6</v>
       </c>
       <c r="F3156" t="n">
         <v>33873</v>
@@ -63578,13 +63578,33 @@
         <v>99.40000000000001</v>
       </c>
       <c r="D3158" t="n">
-        <v>99.05</v>
+        <v>98.34999999999999</v>
       </c>
       <c r="E3158" t="n">
-        <v>99.05</v>
+        <v>98.40000000000001</v>
       </c>
       <c r="F3158" t="n">
-        <v>2906</v>
+        <v>14489</v>
+      </c>
+    </row>
+    <row r="3159">
+      <c r="A3159" s="1" t="n">
+        <v>46275</v>
+      </c>
+      <c r="B3159" t="n">
+        <v>98.40000000000001</v>
+      </c>
+      <c r="C3159" t="n">
+        <v>98.40000000000001</v>
+      </c>
+      <c r="D3159" t="n">
+        <v>97.95</v>
+      </c>
+      <c r="E3159" t="n">
+        <v>98.09999999999999</v>
+      </c>
+      <c r="F3159" t="n">
+        <v>2340</v>
       </c>
     </row>
   </sheetData>

--- a/database/FEF1!.xlsx
+++ b/database/FEF1!.xlsx
@@ -417,7 +417,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:F3159"/>
+  <dimension ref="A1:F3160"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -63561,7 +63561,7 @@
         <v>99.09999999999999</v>
       </c>
       <c r="E3157" t="n">
-        <v>99.34999999999999</v>
+        <v>99.36</v>
       </c>
       <c r="F3157" t="n">
         <v>8092</v>
@@ -63581,7 +63581,7 @@
         <v>98.34999999999999</v>
       </c>
       <c r="E3158" t="n">
-        <v>98.40000000000001</v>
+        <v>98.5</v>
       </c>
       <c r="F3158" t="n">
         <v>14489</v>
@@ -63598,13 +63598,33 @@
         <v>98.40000000000001</v>
       </c>
       <c r="D3159" t="n">
-        <v>97.95</v>
+        <v>97.2</v>
       </c>
       <c r="E3159" t="n">
-        <v>98.09999999999999</v>
+        <v>97.45</v>
       </c>
       <c r="F3159" t="n">
-        <v>2340</v>
+        <v>18065</v>
+      </c>
+    </row>
+    <row r="3160">
+      <c r="A3160" s="1" t="n">
+        <v>46276</v>
+      </c>
+      <c r="B3160" t="n">
+        <v>97.45</v>
+      </c>
+      <c r="C3160" t="n">
+        <v>97.55</v>
+      </c>
+      <c r="D3160" t="n">
+        <v>97.15000000000001</v>
+      </c>
+      <c r="E3160" t="n">
+        <v>97.25</v>
+      </c>
+      <c r="F3160" t="n">
+        <v>866</v>
       </c>
     </row>
   </sheetData>
